--- a/AMAT.xlsx
+++ b/AMAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EE1569-01C8-43B1-A0DB-88A0D813F1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DD1B2E-0627-43C6-BF36-AE52BD7AD27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42170" yWindow="2090" windowWidth="31080" windowHeight="16810" xr2:uid="{8FCE8A41-16C1-4EF7-92D6-76FBB8A04D3E}"/>
+    <workbookView xWindow="5780" yWindow="4160" windowWidth="23600" windowHeight="13830" xr2:uid="{8FCE8A41-16C1-4EF7-92D6-76FBB8A04D3E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="87">
   <si>
     <t>Price</t>
   </si>
@@ -261,9 +261,6 @@
     <t>Net Cash</t>
   </si>
   <si>
-    <t>Q424</t>
-  </si>
-  <si>
     <t>Epitaxy (or epi) is a technique for growing silicon (e.g. silicon with another element) as a uniform crystalline structure on a wafer to form high quality material for the device circuity. Epi technology is used in device transistors to enhance chip speed.</t>
   </si>
   <si>
@@ -295,6 +292,12 @@
   </si>
   <si>
     <t>FCF</t>
+  </si>
+  <si>
+    <t>CIC</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -443,15 +446,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>27774</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>32658</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>27774</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>32658</xdr:colOff>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>161192</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -467,7 +470,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6475466" y="0"/>
+          <a:off x="7823620" y="0"/>
           <a:ext cx="0" cy="12275038"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -493,15 +496,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>4053</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>24319</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>4053</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>60403</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -875,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>228</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -886,10 +889,10 @@
         <v>1</v>
       </c>
       <c r="K3" s="2">
-        <v>812.44084899999996</v>
+        <v>799</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
@@ -898,7 +901,7 @@
       </c>
       <c r="K4" s="2">
         <f>+K2*K3</f>
-        <v>185236.513572</v>
+        <v>287640</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -909,10 +912,10 @@
         <v>3</v>
       </c>
       <c r="K5" s="2">
-        <v>10899</v>
+        <v>13479</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
@@ -923,10 +926,10 @@
         <v>4</v>
       </c>
       <c r="K6" s="2">
-        <v>6260</v>
+        <v>6553</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
@@ -938,7 +941,7 @@
       </c>
       <c r="K7" s="2">
         <f>+K4-K5+K6</f>
-        <v>180597.513572</v>
+        <v>280714</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -989,52 +992,52 @@
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1045,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0FCC328-206B-416D-93E7-7AB15E2A4BC1}">
-  <dimension ref="A1:AR71"/>
+  <dimension ref="A1:AV72"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1053,12 +1056,12 @@
     <col min="7" max="10" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:44" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:48" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C2" s="4">
         <v>45319</v>
       </c>
@@ -1075,231 +1078,239 @@
       <c r="I2" s="4">
         <v>45865</v>
       </c>
-      <c r="M2" s="6">
-        <f t="shared" ref="M2:P2" si="0">+N2-1</f>
+      <c r="J2" s="4">
+        <f>+I2+91</f>
+        <v>45956</v>
+      </c>
+      <c r="K2" s="4">
+        <f>+J2+91</f>
+        <v>46047</v>
+      </c>
+      <c r="Q2" s="6">
+        <f t="shared" ref="Q2:T2" si="0">+R2-1</f>
         <v>2005</v>
       </c>
-      <c r="N2" s="6">
+      <c r="R2" s="6">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="O2" s="6">
+      <c r="S2" s="6">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="P2" s="6">
+      <c r="T2" s="6">
         <f t="shared" si="0"/>
         <v>2008</v>
       </c>
-      <c r="Q2" s="6">
-        <f t="shared" ref="Q2:T2" si="1">+R2-1</f>
+      <c r="U2" s="6">
+        <f t="shared" ref="U2:X2" si="1">+V2-1</f>
         <v>2009</v>
       </c>
-      <c r="R2" s="6">
+      <c r="V2" s="6">
         <f t="shared" si="1"/>
         <v>2010</v>
       </c>
-      <c r="S2" s="6">
+      <c r="W2" s="6">
         <f t="shared" si="1"/>
         <v>2011</v>
       </c>
-      <c r="T2" s="6">
+      <c r="X2" s="6">
         <f t="shared" si="1"/>
         <v>2012</v>
       </c>
-      <c r="U2" s="6">
-        <f>+V2-1</f>
+      <c r="Y2" s="6">
+        <f>+Z2-1</f>
         <v>2013</v>
       </c>
-      <c r="V2" s="6">
+      <c r="Z2" s="6">
         <v>2014</v>
       </c>
-      <c r="W2" s="6">
+      <c r="AA2" s="6">
         <v>2015</v>
       </c>
-      <c r="X2" s="6">
+      <c r="AB2" s="6">
         <v>2016</v>
       </c>
-      <c r="Y2" s="6">
+      <c r="AC2" s="6">
         <v>2017</v>
       </c>
-      <c r="Z2" s="6">
+      <c r="AD2" s="6">
         <v>2018</v>
       </c>
-      <c r="AA2" s="6">
+      <c r="AE2" s="6">
         <v>2019</v>
       </c>
-      <c r="AB2" s="6">
+      <c r="AF2" s="6">
         <v>2020</v>
       </c>
-      <c r="AC2" s="6">
+      <c r="AG2" s="6">
         <v>2021</v>
       </c>
-      <c r="AD2" s="6">
+      <c r="AH2" s="6">
         <v>2022</v>
       </c>
-      <c r="AE2" s="6">
+      <c r="AI2" s="6">
         <v>2023</v>
       </c>
-      <c r="AF2" s="6">
+      <c r="AJ2" s="6">
         <v>2024</v>
       </c>
-      <c r="AG2" s="6">
-        <f t="shared" ref="AG2:AR2" si="2">+AF2+1</f>
+      <c r="AK2" s="6">
+        <f t="shared" ref="AK2:AV2" si="2">+AJ2+1</f>
         <v>2025</v>
       </c>
-      <c r="AH2" s="6">
+      <c r="AL2" s="6">
         <f t="shared" si="2"/>
         <v>2026</v>
       </c>
-      <c r="AI2" s="6">
+      <c r="AM2" s="6">
         <f t="shared" si="2"/>
         <v>2027</v>
       </c>
-      <c r="AJ2" s="6">
+      <c r="AN2" s="6">
         <f t="shared" si="2"/>
         <v>2028</v>
       </c>
-      <c r="AK2" s="6">
+      <c r="AO2" s="6">
         <f t="shared" si="2"/>
         <v>2029</v>
       </c>
-      <c r="AL2" s="6">
+      <c r="AP2" s="6">
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
-      <c r="AM2" s="6">
+      <c r="AQ2" s="6">
         <f t="shared" si="2"/>
         <v>2031</v>
       </c>
-      <c r="AN2" s="6">
+      <c r="AR2" s="6">
         <f t="shared" si="2"/>
         <v>2032</v>
       </c>
-      <c r="AO2" s="6">
+      <c r="AS2" s="6">
         <f t="shared" si="2"/>
         <v>2033</v>
       </c>
-      <c r="AP2" s="6">
+      <c r="AT2" s="6">
         <f t="shared" si="2"/>
         <v>2034</v>
       </c>
-      <c r="AQ2" s="6">
+      <c r="AU2" s="6">
         <f t="shared" si="2"/>
         <v>2035</v>
       </c>
-      <c r="AR2" s="6">
+      <c r="AV2" s="6">
         <f t="shared" si="2"/>
         <v>2036</v>
       </c>
     </row>
-    <row r="3" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AE3" s="2">
+      <c r="AI3" s="2">
         <v>7247</v>
       </c>
-      <c r="AF3" s="2">
+      <c r="AJ3" s="2">
         <v>10117</v>
       </c>
     </row>
-    <row r="4" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AE4" s="2">
+      <c r="AI4" s="2">
         <v>4609</v>
       </c>
-      <c r="AF4" s="2">
+      <c r="AJ4" s="2">
         <v>4493</v>
       </c>
     </row>
-    <row r="5" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AE5" s="2">
+      <c r="AI5" s="2">
         <v>5670</v>
       </c>
-      <c r="AF5" s="2">
+      <c r="AJ5" s="2">
         <v>4010</v>
       </c>
     </row>
-    <row r="6" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AE6" s="2">
+      <c r="AI6" s="2">
         <v>4006</v>
       </c>
-      <c r="AF6" s="2">
+      <c r="AJ6" s="2">
         <v>3818</v>
       </c>
     </row>
-    <row r="7" spans="1:44" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-    </row>
-    <row r="8" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:48" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI7" s="6"/>
+      <c r="AJ7" s="6"/>
+    </row>
+    <row r="8" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AE8" s="2">
+      <c r="AI8" s="2">
         <v>11127</v>
       </c>
-      <c r="AF8" s="2">
+      <c r="AJ8" s="2">
         <v>8259</v>
       </c>
     </row>
-    <row r="9" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AE9" s="2">
+      <c r="AI9" s="2">
         <v>5162</v>
       </c>
-      <c r="AF9" s="2">
+      <c r="AJ9" s="2">
         <v>6767</v>
       </c>
     </row>
-    <row r="10" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AE11" s="2">
+      <c r="AI11" s="2">
         <v>19698</v>
       </c>
-      <c r="AF11" s="2">
+      <c r="AJ11" s="2">
         <v>19911</v>
       </c>
     </row>
-    <row r="12" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AE12" s="2">
+      <c r="AI12" s="2">
         <v>5732</v>
       </c>
-      <c r="AF12" s="2">
+      <c r="AJ12" s="2">
         <v>6225</v>
       </c>
     </row>
-    <row r="13" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AE13" s="2">
+      <c r="AI13" s="2">
         <f>868+219</f>
         <v>1087</v>
       </c>
-      <c r="AF13" s="2">
+      <c r="AJ13" s="2">
         <f>885+155</f>
         <v>1040</v>
       </c>
     </row>
-    <row r="14" spans="1:44" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:48" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>7</v>
       </c>
@@ -1315,67 +1326,70 @@
       <c r="I14" s="7">
         <v>7302</v>
       </c>
-      <c r="N14" s="7">
+      <c r="K14" s="7">
+        <v>7012</v>
+      </c>
+      <c r="R14" s="7">
         <v>9167.0139999999992</v>
       </c>
-      <c r="O14" s="7">
+      <c r="S14" s="7">
         <v>9734.8559999999998</v>
       </c>
-      <c r="P14" s="7">
+      <c r="T14" s="7">
         <v>8129.24</v>
       </c>
-      <c r="Q14" s="7">
+      <c r="U14" s="7">
         <v>5014</v>
       </c>
-      <c r="R14" s="7">
+      <c r="V14" s="7">
         <v>9549</v>
       </c>
-      <c r="S14" s="7">
+      <c r="W14" s="7">
         <v>10517</v>
       </c>
-      <c r="T14" s="7">
+      <c r="X14" s="7">
         <v>8719</v>
       </c>
-      <c r="U14" s="7">
+      <c r="Y14" s="7">
         <v>7509</v>
       </c>
-      <c r="V14" s="7">
+      <c r="Z14" s="7">
         <v>9072</v>
       </c>
-      <c r="W14" s="7">
+      <c r="AA14" s="7">
         <v>9659</v>
       </c>
-      <c r="X14" s="7">
+      <c r="AB14" s="7">
         <v>10825</v>
       </c>
-      <c r="Y14" s="7">
+      <c r="AC14" s="7">
         <v>14537</v>
       </c>
-      <c r="Z14" s="7">
+      <c r="AD14" s="7">
         <v>17253</v>
       </c>
-      <c r="AA14" s="7">
+      <c r="AE14" s="7">
         <v>14608</v>
       </c>
-      <c r="AB14" s="7">
+      <c r="AF14" s="7">
         <v>17202</v>
       </c>
-      <c r="AC14" s="7">
+      <c r="AG14" s="7">
         <v>23063</v>
       </c>
-      <c r="AD14" s="7">
+      <c r="AH14" s="7">
         <v>25785</v>
       </c>
-      <c r="AE14" s="7">
-        <f>SUM(AE11:AE13)</f>
+      <c r="AI14" s="7">
+        <f>SUM(AI11:AI13)</f>
         <v>26517</v>
       </c>
-      <c r="AF14" s="7">
-        <f>SUM(AF11:AF13)</f>
+      <c r="AJ14" s="7">
+        <f>SUM(AJ11:AJ13)</f>
         <v>27176</v>
       </c>
     </row>
-    <row r="15" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
@@ -1391,26 +1405,29 @@
       <c r="I15" s="2">
         <v>3740</v>
       </c>
-      <c r="AA15" s="2">
+      <c r="K15" s="2">
+        <v>3577</v>
+      </c>
+      <c r="AE15" s="2">
         <v>8222</v>
       </c>
-      <c r="AB15" s="2">
+      <c r="AF15" s="2">
         <v>9510</v>
       </c>
-      <c r="AC15" s="2">
+      <c r="AG15" s="2">
         <v>12149</v>
       </c>
-      <c r="AD15" s="2">
+      <c r="AH15" s="2">
         <v>13792</v>
       </c>
-      <c r="AE15" s="2">
+      <c r="AI15" s="2">
         <v>14133</v>
       </c>
-      <c r="AF15" s="2">
+      <c r="AJ15" s="2">
         <v>14279</v>
       </c>
     </row>
-    <row r="16" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1430,32 +1447,36 @@
         <f>+I14-I15</f>
         <v>3562</v>
       </c>
-      <c r="AA16" s="2">
-        <f t="shared" ref="AA16:AF16" si="3">+AA14-AA15</f>
+      <c r="K16" s="2">
+        <f>+K14-K15</f>
+        <v>3435</v>
+      </c>
+      <c r="AE16" s="2">
+        <f t="shared" ref="AE16:AJ16" si="3">+AE14-AE15</f>
         <v>6386</v>
       </c>
-      <c r="AB16" s="2">
+      <c r="AF16" s="2">
         <f t="shared" si="3"/>
         <v>7692</v>
       </c>
-      <c r="AC16" s="2">
+      <c r="AG16" s="2">
         <f t="shared" si="3"/>
         <v>10914</v>
       </c>
-      <c r="AD16" s="2">
+      <c r="AH16" s="2">
         <f t="shared" si="3"/>
         <v>11993</v>
       </c>
-      <c r="AE16" s="2">
+      <c r="AI16" s="2">
         <f t="shared" si="3"/>
         <v>12384</v>
       </c>
-      <c r="AF16" s="2">
+      <c r="AJ16" s="2">
         <f t="shared" si="3"/>
         <v>12897</v>
       </c>
     </row>
-    <row r="17" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
@@ -1471,26 +1492,29 @@
       <c r="I17" s="2">
         <v>901</v>
       </c>
-      <c r="AA17" s="2">
+      <c r="K17" s="2">
+        <v>928</v>
+      </c>
+      <c r="AE17" s="2">
         <v>2054</v>
       </c>
-      <c r="AB17" s="2">
+      <c r="AF17" s="2">
         <v>2234</v>
       </c>
-      <c r="AC17" s="2">
+      <c r="AG17" s="2">
         <v>2485</v>
       </c>
-      <c r="AD17" s="2">
+      <c r="AH17" s="2">
         <v>2771</v>
       </c>
-      <c r="AE17" s="2">
+      <c r="AI17" s="2">
         <v>3102</v>
       </c>
-      <c r="AF17" s="2">
+      <c r="AJ17" s="2">
         <v>3233</v>
       </c>
     </row>
-    <row r="18" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>11</v>
       </c>
@@ -1506,26 +1530,29 @@
       <c r="I18" s="2">
         <v>224</v>
       </c>
-      <c r="AA18" s="2">
+      <c r="K18" s="2">
+        <v>222</v>
+      </c>
+      <c r="AE18" s="2">
         <v>521</v>
       </c>
-      <c r="AB18" s="2">
+      <c r="AF18" s="2">
         <v>526</v>
       </c>
-      <c r="AC18" s="2">
+      <c r="AG18" s="2">
         <v>609</v>
       </c>
-      <c r="AD18" s="2">
+      <c r="AH18" s="2">
         <v>703</v>
       </c>
-      <c r="AE18" s="2">
+      <c r="AI18" s="2">
         <v>776</v>
       </c>
-      <c r="AF18" s="2">
+      <c r="AJ18" s="2">
         <v>836</v>
       </c>
     </row>
-    <row r="19" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
@@ -1541,26 +1568,29 @@
       <c r="I19" s="2">
         <v>204</v>
       </c>
-      <c r="AA19" s="2">
+      <c r="K19" s="2">
+        <v>189</v>
+      </c>
+      <c r="AE19" s="2">
         <v>461</v>
       </c>
-      <c r="AB19" s="2">
+      <c r="AF19" s="2">
         <v>567</v>
       </c>
-      <c r="AC19" s="2">
+      <c r="AG19" s="2">
         <v>620</v>
       </c>
-      <c r="AD19" s="2">
+      <c r="AH19" s="2">
         <v>735</v>
       </c>
-      <c r="AE19" s="2">
+      <c r="AI19" s="2">
         <v>852</v>
       </c>
-      <c r="AF19" s="2">
+      <c r="AJ19" s="2">
         <v>961</v>
       </c>
     </row>
-    <row r="20" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
@@ -1589,42 +1619,49 @@
         <f>SUM(I17:I19)</f>
         <v>1329</v>
       </c>
-      <c r="J20" s="2"/>
-      <c r="AA20" s="2">
-        <f t="shared" ref="AA20:AC20" si="5">SUM(AA17:AA19)</f>
+      <c r="J20" s="2">
+        <f t="shared" ref="J20:K20" si="5">SUM(J17:J19)</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <f t="shared" si="5"/>
+        <v>1339</v>
+      </c>
+      <c r="AE20" s="2">
+        <f t="shared" ref="AE20:AG20" si="6">SUM(AE17:AE19)</f>
         <v>3036</v>
       </c>
-      <c r="AB20" s="2">
-        <f t="shared" si="5"/>
+      <c r="AF20" s="2">
+        <f t="shared" si="6"/>
         <v>3327</v>
       </c>
-      <c r="AC20" s="2">
-        <f t="shared" si="5"/>
+      <c r="AG20" s="2">
+        <f t="shared" si="6"/>
         <v>3714</v>
       </c>
-      <c r="AD20" s="2">
-        <f>SUM(AD17:AD19)</f>
+      <c r="AH20" s="2">
+        <f>SUM(AH17:AH19)</f>
         <v>4209</v>
       </c>
-      <c r="AE20" s="2">
-        <f>SUM(AE17:AE19)</f>
+      <c r="AI20" s="2">
+        <f>SUM(AI17:AI19)</f>
         <v>4730</v>
       </c>
-      <c r="AF20" s="2">
-        <f>SUM(AF17:AF19)</f>
+      <c r="AJ20" s="2">
+        <f>SUM(AJ17:AJ19)</f>
         <v>5030</v>
       </c>
     </row>
-    <row r="21" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" ref="C21:F21" si="6">C16-C20</f>
+        <f t="shared" ref="C21:F21" si="7">C16-C20</f>
         <v>1967</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E21" s="2">
@@ -1632,7 +1669,7 @@
         <v>1942</v>
       </c>
       <c r="F21" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G21" s="2">
@@ -1644,33 +1681,40 @@
         <f>I16-I20</f>
         <v>2233</v>
       </c>
-      <c r="J21" s="2"/>
-      <c r="AA21" s="2">
-        <f t="shared" ref="AA21:AC21" si="7">AA16-AA20</f>
+      <c r="J21" s="2">
+        <f t="shared" ref="J21:K21" si="8">J16-J20</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <f t="shared" si="8"/>
+        <v>2096</v>
+      </c>
+      <c r="AE21" s="2">
+        <f t="shared" ref="AE21:AG21" si="9">AE16-AE20</f>
         <v>3350</v>
       </c>
-      <c r="AB21" s="2">
-        <f t="shared" si="7"/>
+      <c r="AF21" s="2">
+        <f t="shared" si="9"/>
         <v>4365</v>
       </c>
-      <c r="AC21" s="2">
-        <f t="shared" si="7"/>
+      <c r="AG21" s="2">
+        <f t="shared" si="9"/>
         <v>7200</v>
       </c>
-      <c r="AD21" s="2">
-        <f>AD16-AD20</f>
+      <c r="AH21" s="2">
+        <f>AH16-AH20</f>
         <v>7784</v>
       </c>
-      <c r="AE21" s="2">
-        <f>AE16-AE20</f>
+      <c r="AI21" s="2">
+        <f>AI16-AI20</f>
         <v>7654</v>
       </c>
-      <c r="AF21" s="2">
-        <f>AF16-AF20</f>
+      <c r="AJ21" s="2">
+        <f>AJ16-AJ20</f>
         <v>7867</v>
       </c>
     </row>
-    <row r="22" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>18</v>
       </c>
@@ -1688,41 +1732,44 @@
         <v>66</v>
       </c>
       <c r="J22" s="2"/>
-      <c r="AA22">
+      <c r="K22" s="2">
+        <v>-69</v>
+      </c>
+      <c r="AE22">
         <f>-237+156</f>
         <v>-81</v>
       </c>
-      <c r="AB22">
+      <c r="AF22">
         <f>-240+41</f>
         <v>-199</v>
       </c>
-      <c r="AC22">
+      <c r="AG22">
         <f>-236+118</f>
         <v>-118</v>
       </c>
-      <c r="AD22" s="2">
+      <c r="AH22" s="2">
         <f>-228+39</f>
         <v>-189</v>
       </c>
-      <c r="AE22" s="2">
+      <c r="AI22" s="2">
         <f>-238+300</f>
         <v>62</v>
       </c>
-      <c r="AF22" s="2">
+      <c r="AJ22" s="2">
         <f>-247+532</f>
         <v>285</v>
       </c>
     </row>
-    <row r="23" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" ref="C23:F23" si="8">+C21+C22</f>
+        <f t="shared" ref="C23:F23" si="10">+C21+C22</f>
         <v>1908</v>
       </c>
       <c r="D23" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E23" s="2">
@@ -1730,7 +1777,7 @@
         <v>1879</v>
       </c>
       <c r="F23" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G23" s="2">
@@ -1742,33 +1789,40 @@
         <f>+I21+I22</f>
         <v>2299</v>
       </c>
-      <c r="J23" s="2"/>
-      <c r="AA23" s="2">
-        <f t="shared" ref="AA23" si="9">+AA21+AA22</f>
+      <c r="J23" s="2">
+        <f t="shared" ref="J23:K23" si="11">+J21+J22</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="2">
+        <f t="shared" si="11"/>
+        <v>2027</v>
+      </c>
+      <c r="AE23" s="2">
+        <f t="shared" ref="AE23" si="12">+AE21+AE22</f>
         <v>3269</v>
       </c>
-      <c r="AB23" s="2">
-        <f t="shared" ref="AB23" si="10">+AB21+AB22</f>
+      <c r="AF23" s="2">
+        <f t="shared" ref="AF23" si="13">+AF21+AF22</f>
         <v>4166</v>
       </c>
-      <c r="AC23" s="2">
-        <f t="shared" ref="AC23" si="11">+AC21+AC22</f>
+      <c r="AG23" s="2">
+        <f t="shared" ref="AG23" si="14">+AG21+AG22</f>
         <v>7082</v>
       </c>
-      <c r="AD23" s="2">
-        <f t="shared" ref="AD23:AF23" si="12">+AD21+AD22</f>
+      <c r="AH23" s="2">
+        <f t="shared" ref="AH23:AJ23" si="15">+AH21+AH22</f>
         <v>7595</v>
       </c>
-      <c r="AE23" s="2">
-        <f t="shared" si="12"/>
+      <c r="AI23" s="2">
+        <f t="shared" si="15"/>
         <v>7716</v>
       </c>
-      <c r="AF23" s="2">
-        <f t="shared" si="12"/>
+      <c r="AJ23" s="2">
+        <f t="shared" si="15"/>
         <v>8152</v>
       </c>
     </row>
-    <row r="24" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>20</v>
       </c>
@@ -1784,35 +1838,38 @@
       <c r="I24" s="2">
         <v>784</v>
       </c>
-      <c r="AA24" s="2">
+      <c r="K24" s="2">
+        <v>302</v>
+      </c>
+      <c r="AE24" s="2">
         <v>563</v>
       </c>
-      <c r="AB24" s="2">
+      <c r="AF24" s="2">
         <v>547</v>
       </c>
-      <c r="AC24" s="2">
+      <c r="AG24" s="2">
         <v>883</v>
       </c>
-      <c r="AD24" s="2">
+      <c r="AH24" s="2">
         <v>1074</v>
       </c>
-      <c r="AE24" s="2">
+      <c r="AI24" s="2">
         <v>860</v>
       </c>
-      <c r="AF24" s="2">
+      <c r="AJ24" s="2">
         <v>975</v>
       </c>
     </row>
-    <row r="25" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="2">
-        <f t="shared" ref="C25:F25" si="13">+C23-C24</f>
+        <f t="shared" ref="C25:F25" si="16">+C23-C24</f>
         <v>1624</v>
       </c>
       <c r="D25" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="E25" s="2">
@@ -1820,7 +1877,7 @@
         <v>1624</v>
       </c>
       <c r="F25" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G25" s="2">
@@ -1832,33 +1889,40 @@
         <f>+I23-I24</f>
         <v>1515</v>
       </c>
-      <c r="J25" s="2"/>
-      <c r="AA25" s="2">
-        <f t="shared" ref="AA25" si="14">+AA23-AA24</f>
+      <c r="J25" s="2">
+        <f t="shared" ref="J25:K25" si="17">+J23-J24</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <f t="shared" si="17"/>
+        <v>1725</v>
+      </c>
+      <c r="AE25" s="2">
+        <f t="shared" ref="AE25" si="18">+AE23-AE24</f>
         <v>2706</v>
       </c>
-      <c r="AB25" s="2">
-        <f t="shared" ref="AB25" si="15">+AB23-AB24</f>
+      <c r="AF25" s="2">
+        <f t="shared" ref="AF25" si="19">+AF23-AF24</f>
         <v>3619</v>
       </c>
-      <c r="AC25" s="2">
-        <f t="shared" ref="AC25" si="16">+AC23-AC24</f>
+      <c r="AG25" s="2">
+        <f t="shared" ref="AG25" si="20">+AG23-AG24</f>
         <v>6199</v>
       </c>
-      <c r="AD25" s="2">
-        <f t="shared" ref="AD25:AF25" si="17">+AD23-AD24</f>
+      <c r="AH25" s="2">
+        <f t="shared" ref="AH25:AJ25" si="21">+AH23-AH24</f>
         <v>6521</v>
       </c>
-      <c r="AE25" s="2">
-        <f t="shared" si="17"/>
+      <c r="AI25" s="2">
+        <f t="shared" si="21"/>
         <v>6856</v>
       </c>
-      <c r="AF25" s="2">
-        <f t="shared" si="17"/>
+      <c r="AJ25" s="2">
+        <f t="shared" si="21"/>
         <v>7177</v>
       </c>
     </row>
-    <row r="26" spans="2:32" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:36" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>22</v>
       </c>
@@ -1867,53 +1931,60 @@
         <v>1.94026284348865</v>
       </c>
       <c r="D26" s="9" t="e">
-        <f t="shared" ref="D26:G26" si="18">+D25/D27</f>
+        <f t="shared" ref="D26:G26" si="22">+D25/D27</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" ref="E26" si="19">+E25/E27</f>
+        <f t="shared" ref="E26" si="23">+E25/E27</f>
         <v>1.9495798319327731</v>
       </c>
       <c r="F26" s="9" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1.4371184371184371</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="9">
-        <f t="shared" ref="I26" si="20">+I25/I27</f>
+        <f t="shared" ref="I26:K26" si="24">+I25/I27</f>
         <v>1.8890274314214464</v>
       </c>
-      <c r="J26" s="9"/>
-      <c r="AA26" s="9">
-        <f t="shared" ref="AA26:AC26" si="21">+AA25/AA27</f>
+      <c r="J26" s="9" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" si="24"/>
+        <v>2.1589486858573217</v>
+      </c>
+      <c r="AE26" s="9">
+        <f t="shared" ref="AE26:AG26" si="25">+AE25/AE27</f>
         <v>2.8634920634920635</v>
       </c>
-      <c r="AB26" s="9">
-        <f t="shared" si="21"/>
+      <c r="AF26" s="9">
+        <f t="shared" si="25"/>
         <v>3.9209100758396533</v>
       </c>
-      <c r="AC26" s="9">
-        <f t="shared" si="21"/>
+      <c r="AG26" s="9">
+        <f t="shared" si="25"/>
         <v>6.7453754080522303</v>
       </c>
-      <c r="AD26" s="9">
-        <f>+AD25/AD27</f>
+      <c r="AH26" s="9">
+        <f>+AH25/AH27</f>
         <v>7.4355758266818697</v>
       </c>
-      <c r="AE26" s="9">
-        <f>+AE25/AE27</f>
+      <c r="AI26" s="9">
+        <f>+AI25/AI27</f>
         <v>8.1136094674556212</v>
       </c>
-      <c r="AF26" s="9">
-        <f>+AF25/AF27</f>
+      <c r="AJ26" s="9">
+        <f>+AJ25/AJ27</f>
         <v>8.6055155875299754</v>
       </c>
     </row>
-    <row r="27" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>1</v>
       </c>
@@ -1933,26 +2004,29 @@
         <v>802</v>
       </c>
       <c r="J27" s="2"/>
-      <c r="AA27">
+      <c r="K27" s="2">
+        <v>799</v>
+      </c>
+      <c r="AE27">
         <v>945</v>
       </c>
-      <c r="AB27">
+      <c r="AF27">
         <v>923</v>
       </c>
-      <c r="AC27">
+      <c r="AG27">
         <v>919</v>
       </c>
-      <c r="AD27">
+      <c r="AH27">
         <v>877</v>
       </c>
-      <c r="AE27">
+      <c r="AI27">
         <v>845</v>
       </c>
-      <c r="AF27">
+      <c r="AJ27">
         <v>834</v>
       </c>
     </row>
-    <row r="29" spans="2:32" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:36" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B29" s="10" t="s">
         <v>13</v>
       </c>
@@ -1965,81 +2039,88 @@
         <f>+I14/E14-1</f>
         <v>7.730894069046923E-2</v>
       </c>
-      <c r="J29" s="11"/>
-      <c r="O29" s="11">
-        <f t="shared" ref="O29:V29" si="22">+O14/N14-1</f>
+      <c r="J29" s="11" t="e">
+        <f>+J14/F14-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K29" s="11">
+        <f>+K14/G14-1</f>
+        <v>-2.1490371197320668E-2</v>
+      </c>
+      <c r="S29" s="11">
+        <f t="shared" ref="S29:Z29" si="26">+S14/R14-1</f>
         <v>6.1944052883523559E-2</v>
       </c>
-      <c r="P29" s="11">
-        <f t="shared" si="22"/>
+      <c r="T29" s="11">
+        <f t="shared" si="26"/>
         <v>-0.16493474582469425</v>
       </c>
-      <c r="Q29" s="11">
-        <f t="shared" si="22"/>
+      <c r="U29" s="11">
+        <f t="shared" si="26"/>
         <v>-0.38321417500282928</v>
       </c>
-      <c r="R29" s="11">
-        <f t="shared" si="22"/>
+      <c r="V29" s="11">
+        <f t="shared" si="26"/>
         <v>0.90446749102512958</v>
       </c>
-      <c r="S29" s="11">
-        <f t="shared" si="22"/>
+      <c r="W29" s="11">
+        <f t="shared" si="26"/>
         <v>0.10137187140014658</v>
       </c>
-      <c r="T29" s="11">
-        <f t="shared" si="22"/>
+      <c r="X29" s="11">
+        <f t="shared" si="26"/>
         <v>-0.17096130075116478</v>
       </c>
-      <c r="U29" s="11">
-        <f t="shared" si="22"/>
+      <c r="Y29" s="11">
+        <f t="shared" si="26"/>
         <v>-0.13877738272737694</v>
       </c>
-      <c r="V29" s="11">
-        <f t="shared" si="22"/>
+      <c r="Z29" s="11">
+        <f t="shared" si="26"/>
         <v>0.20815021973631631</v>
       </c>
-      <c r="W29" s="11">
-        <f t="shared" ref="W29:AA29" si="23">+W14/V14-1</f>
+      <c r="AA29" s="11">
+        <f t="shared" ref="AA29:AE29" si="27">+AA14/Z14-1</f>
         <v>6.4704585537918913E-2</v>
       </c>
-      <c r="X29" s="11">
-        <f t="shared" si="23"/>
+      <c r="AB29" s="11">
+        <f t="shared" si="27"/>
         <v>0.12071643027228496</v>
       </c>
-      <c r="Y29" s="11">
-        <f t="shared" si="23"/>
+      <c r="AC29" s="11">
+        <f t="shared" si="27"/>
         <v>0.34290993071593534</v>
       </c>
-      <c r="Z29" s="11">
-        <f t="shared" si="23"/>
+      <c r="AD29" s="11">
+        <f t="shared" si="27"/>
         <v>0.18683359702827262</v>
       </c>
-      <c r="AA29" s="11">
-        <f t="shared" si="23"/>
+      <c r="AE29" s="11">
+        <f t="shared" si="27"/>
         <v>-0.15330667130354136</v>
       </c>
-      <c r="AB29" s="11">
-        <f t="shared" ref="AB29:AD29" si="24">+AB14/AA14-1</f>
+      <c r="AF29" s="11">
+        <f t="shared" ref="AF29:AH29" si="28">+AF14/AE14-1</f>
         <v>0.17757393209200445</v>
       </c>
-      <c r="AC29" s="11">
-        <f t="shared" si="24"/>
+      <c r="AG29" s="11">
+        <f t="shared" si="28"/>
         <v>0.34071619579118706</v>
       </c>
-      <c r="AD29" s="11">
-        <f t="shared" si="24"/>
+      <c r="AH29" s="11">
+        <f t="shared" si="28"/>
         <v>0.11802454147335562</v>
       </c>
-      <c r="AE29" s="3">
-        <f>+AE14/AD14-1</f>
+      <c r="AI29" s="3">
+        <f>+AI14/AH14-1</f>
         <v>2.8388598022105915E-2</v>
       </c>
-      <c r="AF29" s="3">
-        <f>+AF14/AE14-1</f>
+      <c r="AJ29" s="3">
+        <f>+AJ14/AI14-1</f>
         <v>2.4851981747558094E-2</v>
       </c>
     </row>
-    <row r="30" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>60</v>
       </c>
@@ -2047,12 +2128,12 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="AF30" s="3">
-        <f>+AF11/AE11-1</f>
+      <c r="AJ30" s="3">
+        <f>+AJ11/AI11-1</f>
         <v>1.0813280536094982E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>14</v>
       </c>
@@ -2067,52 +2148,56 @@
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
-      <c r="V31" s="3">
-        <f t="shared" ref="V31:Z31" si="25">+V16/V14</f>
-        <v>0</v>
-      </c>
-      <c r="W31" s="3">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X31" s="3">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
       <c r="Z31" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="Z31:AD31" si="29">+Z16/Z14</f>
         <v>0</v>
       </c>
       <c r="AA31" s="3">
-        <f t="shared" ref="AA31:AC31" si="26">+AA16/AA14</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <f t="shared" ref="AE31:AG31" si="30">+AE16/AE14</f>
         <v>0.43715772179627599</v>
       </c>
-      <c r="AB31" s="3">
-        <f t="shared" si="26"/>
+      <c r="AF31" s="3">
+        <f t="shared" si="30"/>
         <v>0.44715730728985004</v>
       </c>
-      <c r="AC31" s="3">
-        <f t="shared" si="26"/>
+      <c r="AG31" s="3">
+        <f t="shared" si="30"/>
         <v>0.47322551272601138</v>
       </c>
-      <c r="AD31" s="3">
-        <f>+AD16/AD14</f>
+      <c r="AH31" s="3">
+        <f>+AH16/AH14</f>
         <v>0.46511537715726198</v>
       </c>
-      <c r="AE31" s="3">
-        <f>+AE16/AE14</f>
+      <c r="AI31" s="3">
+        <f>+AI16/AI14</f>
         <v>0.46702115623939361</v>
       </c>
-      <c r="AF31" s="3">
-        <f>+AF16/AF14</f>
+      <c r="AJ31" s="3">
+        <f>+AJ16/AJ14</f>
         <v>0.47457315278186635</v>
       </c>
     </row>
-    <row r="32" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>15</v>
       </c>
@@ -2127,52 +2212,56 @@
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
-      <c r="V32" s="3">
-        <f t="shared" ref="V32:Z32" si="27">+V21/V14</f>
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
       <c r="Z32" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="Z32:AD32" si="31">+Z21/Z14</f>
         <v>0</v>
       </c>
       <c r="AA32" s="3">
-        <f t="shared" ref="AA32:AC32" si="28">+AA21/AA14</f>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <f t="shared" ref="AE32:AG32" si="32">+AE21/AE14</f>
         <v>0.22932639649507119</v>
       </c>
-      <c r="AB32" s="3">
-        <f t="shared" si="28"/>
+      <c r="AF32" s="3">
+        <f t="shared" si="32"/>
         <v>0.25374956400418558</v>
       </c>
-      <c r="AC32" s="3">
-        <f t="shared" si="28"/>
+      <c r="AG32" s="3">
+        <f t="shared" si="32"/>
         <v>0.3121883536400295</v>
       </c>
-      <c r="AD32" s="3">
-        <f>+AD21/AD14</f>
+      <c r="AH32" s="3">
+        <f>+AH21/AH14</f>
         <v>0.30188093853015319</v>
       </c>
-      <c r="AE32" s="3">
-        <f>+AE21/AE14</f>
+      <c r="AI32" s="3">
+        <f>+AI21/AI14</f>
         <v>0.28864502017573634</v>
       </c>
-      <c r="AF32" s="3">
-        <f>+AF21/AF14</f>
+      <c r="AJ32" s="3">
+        <f>+AJ21/AJ14</f>
         <v>0.28948336767736238</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>73</v>
       </c>
@@ -2192,9 +2281,16 @@
         <f>+I35-I44</f>
         <v>4885</v>
       </c>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J34" s="2">
+        <f>+J35-J44</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="2">
+        <f>+K35-K44</f>
+        <v>6926</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>3</v>
       </c>
@@ -2210,8 +2306,12 @@
         <f>5384+1630+4133</f>
         <v>11147</v>
       </c>
-    </row>
-    <row r="36" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K35" s="2">
+        <f>7218+1293+4968</f>
+        <v>13479</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>24</v>
       </c>
@@ -2224,8 +2324,11 @@
       <c r="I36" s="2">
         <v>5772</v>
       </c>
-    </row>
-    <row r="37" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K36" s="2">
+        <v>4977</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>25</v>
       </c>
@@ -2238,8 +2341,11 @@
       <c r="I37" s="2">
         <v>5807</v>
       </c>
-    </row>
-    <row r="38" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K37" s="2">
+        <v>5997</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>26</v>
       </c>
@@ -2252,8 +2358,11 @@
       <c r="I38" s="2">
         <v>1125</v>
       </c>
-    </row>
-    <row r="39" spans="2:10" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="K38" s="2">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B39" s="7" t="s">
         <v>23</v>
       </c>
@@ -2266,8 +2375,11 @@
       <c r="I39" s="7">
         <v>4124</v>
       </c>
-    </row>
-    <row r="40" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K39" s="7">
+        <v>4949</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>27</v>
       </c>
@@ -2283,8 +2395,12 @@
         <f>3748+238</f>
         <v>3986</v>
       </c>
-    </row>
-    <row r="41" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K40" s="2">
+        <f>3707+215</f>
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>28</v>
       </c>
@@ -2297,8 +2413,11 @@
       <c r="I41" s="2">
         <v>2250</v>
       </c>
-    </row>
-    <row r="42" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K41" s="2">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
         <v>29</v>
       </c>
@@ -2318,8 +2437,16 @@
         <f>SUM(I35:I41)</f>
         <v>34211</v>
       </c>
-    </row>
-    <row r="44" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J42" s="2">
+        <f>SUM(J35:J41)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="2">
+        <f>SUM(K35:K41)</f>
+        <v>37644</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>4</v>
       </c>
@@ -2331,8 +2458,11 @@
         <f>5463+799</f>
         <v>6262</v>
       </c>
-    </row>
-    <row r="45" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K44" s="2">
+        <v>6553</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>30</v>
       </c>
@@ -2342,8 +2472,11 @@
       <c r="I45" s="2">
         <v>4614</v>
       </c>
-    </row>
-    <row r="46" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K45" s="2">
+        <v>5181</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>31</v>
       </c>
@@ -2353,8 +2486,11 @@
       <c r="I46" s="2">
         <v>2470</v>
       </c>
-    </row>
-    <row r="47" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K46" s="2">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
         <v>20</v>
       </c>
@@ -2364,8 +2500,11 @@
       <c r="I47" s="2">
         <v>330</v>
       </c>
-    </row>
-    <row r="48" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K47" s="2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>34</v>
       </c>
@@ -2375,8 +2514,11 @@
       <c r="I48" s="2">
         <v>1031</v>
       </c>
-    </row>
-    <row r="49" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K48" s="2">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="49" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
         <v>32</v>
       </c>
@@ -2386,8 +2528,11 @@
       <c r="I49" s="2">
         <v>19504</v>
       </c>
-    </row>
-    <row r="50" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K49" s="2">
+        <v>21717</v>
+      </c>
+    </row>
+    <row r="50" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
         <v>33</v>
       </c>
@@ -2403,8 +2548,16 @@
         <f>SUM(I44:I49)</f>
         <v>34211</v>
       </c>
-    </row>
-    <row r="52" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J50" s="2">
+        <f>SUM(J44:J49)</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="2">
+        <f>SUM(K44:K49)</f>
+        <v>37644</v>
+      </c>
+    </row>
+    <row r="52" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
         <v>38</v>
       </c>
@@ -2420,93 +2573,117 @@
         <f>+I25</f>
         <v>1515</v>
       </c>
-      <c r="X52" s="2">
-        <f t="shared" ref="X52:Z52" si="29">+X25</f>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="2">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Z52" s="2">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AA52" s="2">
-        <f t="shared" ref="AA52:AF52" si="30">+AA25</f>
+      <c r="J52" s="2">
+        <f>+J25</f>
+        <v>0</v>
+      </c>
+      <c r="K52" s="2">
+        <f>+K25</f>
+        <v>1725</v>
+      </c>
+      <c r="AB52" s="2">
+        <f t="shared" ref="AB52:AD52" si="33">+AB25</f>
+        <v>0</v>
+      </c>
+      <c r="AC52" s="2">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AD52" s="2">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AE52" s="2">
+        <f t="shared" ref="AE52:AJ52" si="34">+AE25</f>
         <v>2706</v>
       </c>
-      <c r="AB52" s="2">
-        <f t="shared" si="30"/>
+      <c r="AF52" s="2">
+        <f t="shared" si="34"/>
         <v>3619</v>
       </c>
-      <c r="AC52" s="2">
-        <f t="shared" si="30"/>
+      <c r="AG52" s="2">
+        <f t="shared" si="34"/>
         <v>6199</v>
       </c>
-      <c r="AD52" s="2">
-        <f t="shared" si="30"/>
+      <c r="AH52" s="2">
+        <f t="shared" si="34"/>
         <v>6521</v>
       </c>
-      <c r="AE52" s="2">
-        <f t="shared" si="30"/>
+      <c r="AI52" s="2">
+        <f t="shared" si="34"/>
         <v>6856</v>
       </c>
-      <c r="AF52" s="2">
-        <f t="shared" si="30"/>
+      <c r="AJ52" s="2">
+        <f t="shared" si="34"/>
         <v>7177</v>
       </c>
     </row>
-    <row r="53" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G53" s="2">
         <v>1185</v>
       </c>
-      <c r="AD53" s="2">
+      <c r="K53" s="2">
+        <v>2026</v>
+      </c>
+      <c r="AH53" s="2">
         <v>6525</v>
       </c>
-      <c r="AE53" s="2">
+      <c r="AI53" s="2">
         <v>6856</v>
       </c>
-      <c r="AF53" s="2">
+      <c r="AJ53" s="2">
         <v>7177</v>
       </c>
     </row>
-    <row r="54" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
         <v>39</v>
       </c>
       <c r="G54" s="2">
         <v>105</v>
       </c>
-    </row>
-    <row r="55" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K54" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G55" s="2">
         <v>195</v>
       </c>
-    </row>
-    <row r="56" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K55" s="2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G56" s="2">
         <v>668</v>
       </c>
-    </row>
-    <row r="57" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K56" s="2">
+        <v>-78</v>
+      </c>
+    </row>
+    <row r="57" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G57" s="2">
         <v>95</v>
       </c>
-    </row>
-    <row r="58" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K57" s="2">
+        <f>-1+12+253-466</f>
+        <v>-202</v>
+      </c>
+    </row>
+    <row r="58" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>36</v>
       </c>
@@ -2514,8 +2691,12 @@
         <f>-764-80+115-429-397+200+32</f>
         <v>-1323</v>
       </c>
-    </row>
-    <row r="59" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K58" s="2">
+        <f>208-82-154-760-94+481+7</f>
+        <v>-394</v>
+      </c>
+    </row>
+    <row r="59" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
         <v>35</v>
       </c>
@@ -2523,54 +2704,58 @@
         <f>SUM(G53:G58)</f>
         <v>925</v>
       </c>
-      <c r="N59" s="2">
+      <c r="K59" s="2">
+        <f>SUM(K53:K58)</f>
+        <v>1686</v>
+      </c>
+      <c r="R59" s="2">
         <v>1977.1179999999999</v>
       </c>
-      <c r="O59" s="2">
+      <c r="S59" s="2">
         <v>2209.2959999999998</v>
       </c>
-      <c r="P59" s="2">
+      <c r="T59" s="2">
         <v>1710.4680000000001</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="U59" s="2">
         <v>332.66500000000002</v>
       </c>
-      <c r="R59" s="2">
+      <c r="V59" s="2">
         <v>1722.8530000000001</v>
       </c>
-      <c r="X59" s="2">
+      <c r="AB59" s="2">
         <v>2566</v>
       </c>
-      <c r="Y59" s="2">
+      <c r="AC59" s="2">
         <v>3789</v>
       </c>
-      <c r="Z59" s="2">
+      <c r="AD59" s="2">
         <v>3787</v>
       </c>
-      <c r="AA59" s="2">
+      <c r="AE59" s="2">
         <v>3247</v>
       </c>
-      <c r="AB59" s="2">
+      <c r="AF59" s="2">
         <v>3804</v>
       </c>
-      <c r="AC59" s="2">
+      <c r="AG59" s="2">
         <v>5442</v>
       </c>
-      <c r="AD59" s="2">
+      <c r="AH59" s="2">
         <v>5399</v>
       </c>
-      <c r="AE59" s="2">
+      <c r="AI59" s="2">
         <v>8700</v>
       </c>
-      <c r="AF59" s="2">
+      <c r="AJ59" s="2">
         <v>8677</v>
       </c>
     </row>
-    <row r="60" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="AE60" s="2"/>
-      <c r="AF60" s="2"/>
-    </row>
-    <row r="61" spans="2:32" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="AI60" s="2"/>
+      <c r="AJ60" s="2"/>
+    </row>
+    <row r="61" spans="2:36" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B61" s="2" t="s">
         <v>42</v>
       </c>
@@ -2580,58 +2765,64 @@
       <c r="H61" s="7"/>
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
-      <c r="N61" s="2">
+      <c r="K61" s="2">
+        <v>-646</v>
+      </c>
+      <c r="R61" s="2">
         <v>-179.482</v>
       </c>
-      <c r="O61" s="2">
+      <c r="S61" s="2">
         <v>-264.78399999999999</v>
       </c>
-      <c r="P61" s="2">
+      <c r="T61" s="2">
         <v>-287.90600000000001</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="U61" s="2">
         <v>-248.42699999999999</v>
       </c>
-      <c r="R61" s="2">
+      <c r="V61" s="2">
         <v>-169.08099999999999</v>
       </c>
-      <c r="X61" s="2">
+      <c r="AB61" s="2">
         <v>-253</v>
       </c>
-      <c r="Y61" s="2">
+      <c r="AC61" s="2">
         <v>-345</v>
       </c>
-      <c r="Z61" s="2">
+      <c r="AD61" s="2">
         <v>-622</v>
       </c>
-      <c r="AA61" s="2">
+      <c r="AE61" s="2">
         <v>-441</v>
       </c>
-      <c r="AB61" s="2">
+      <c r="AF61" s="2">
         <v>-422</v>
       </c>
-      <c r="AC61" s="2">
+      <c r="AG61" s="2">
         <v>-668</v>
       </c>
-      <c r="AD61" s="2">
+      <c r="AH61" s="2">
         <v>-787</v>
       </c>
-      <c r="AE61" s="2">
+      <c r="AI61" s="2">
         <v>-1106</v>
       </c>
-      <c r="AF61" s="2">
+      <c r="AJ61" s="2">
         <v>-1190</v>
       </c>
     </row>
-    <row r="62" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G62">
         <v>-28</v>
       </c>
-    </row>
-    <row r="63" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="K62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
         <v>44</v>
       </c>
@@ -2639,8 +2830,12 @@
         <f>1223-1711</f>
         <v>-488</v>
       </c>
-    </row>
-    <row r="64" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="K63">
+        <f>1143-1277</f>
+        <v>-134</v>
+      </c>
+    </row>
+    <row r="64" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>41</v>
       </c>
@@ -2648,32 +2843,45 @@
         <f>SUM(G61:G63)</f>
         <v>-897</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K64">
+        <f>SUM(K61:K63)</f>
+        <v>-780</v>
+      </c>
+    </row>
+    <row r="66" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G66" s="2">
         <v>-1318</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K66" s="2">
+        <v>-337</v>
+      </c>
+    </row>
+    <row r="67" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G67" s="2">
         <v>-142</v>
       </c>
-    </row>
-    <row r="68" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K67" s="2">
+        <v>-229</v>
+      </c>
+    </row>
+    <row r="68" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
         <v>48</v>
       </c>
       <c r="G68" s="2">
         <v>-326</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K68" s="2">
+        <v>-365</v>
+      </c>
+    </row>
+    <row r="69" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
         <v>46</v>
       </c>
@@ -2681,65 +2889,94 @@
         <f>SUM(G66:G68)</f>
         <v>-1786</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B71" s="2" t="s">
+      <c r="H69" s="2">
+        <f t="shared" ref="H69:K69" si="35">SUM(H66:H68)</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="2">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="2">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K69" s="2">
+        <f t="shared" si="35"/>
+        <v>-931</v>
+      </c>
+    </row>
+    <row r="70" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="N71" s="2">
-        <f t="shared" ref="N71:R71" si="31">+N59+N61</f>
+      <c r="K70" s="2">
+        <f>+K69+K64+K59</f>
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="72" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B72" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K72" s="2">
+        <f>+K59+K61</f>
+        <v>1040</v>
+      </c>
+      <c r="R72" s="2">
+        <f t="shared" ref="R72:V72" si="36">+R59+R61</f>
         <v>1797.636</v>
       </c>
-      <c r="O71" s="2">
-        <f t="shared" si="31"/>
+      <c r="S72" s="2">
+        <f t="shared" si="36"/>
         <v>1944.5119999999997</v>
       </c>
-      <c r="P71" s="2">
-        <f t="shared" si="31"/>
+      <c r="T72" s="2">
+        <f t="shared" si="36"/>
         <v>1422.5620000000001</v>
       </c>
-      <c r="Q71" s="2">
-        <f t="shared" si="31"/>
+      <c r="U72" s="2">
+        <f t="shared" si="36"/>
         <v>84.238000000000028</v>
       </c>
-      <c r="R71" s="2">
-        <f t="shared" si="31"/>
+      <c r="V72" s="2">
+        <f t="shared" si="36"/>
         <v>1553.7720000000002</v>
       </c>
-      <c r="X71" s="2">
-        <f t="shared" ref="X71:Z71" si="32">+X59+X61</f>
+      <c r="AB72" s="2">
+        <f t="shared" ref="AB72:AD72" si="37">+AB59+AB61</f>
         <v>2313</v>
       </c>
-      <c r="Y71" s="2">
-        <f t="shared" si="32"/>
+      <c r="AC72" s="2">
+        <f t="shared" si="37"/>
         <v>3444</v>
       </c>
-      <c r="Z71" s="2">
-        <f t="shared" si="32"/>
+      <c r="AD72" s="2">
+        <f t="shared" si="37"/>
         <v>3165</v>
       </c>
-      <c r="AA71" s="2">
-        <f t="shared" ref="AA71:AF71" si="33">+AA59+AA61</f>
+      <c r="AE72" s="2">
+        <f t="shared" ref="AE72:AJ72" si="38">+AE59+AE61</f>
         <v>2806</v>
       </c>
-      <c r="AB71" s="2">
-        <f t="shared" si="33"/>
+      <c r="AF72" s="2">
+        <f t="shared" si="38"/>
         <v>3382</v>
       </c>
-      <c r="AC71" s="2">
-        <f t="shared" si="33"/>
+      <c r="AG72" s="2">
+        <f t="shared" si="38"/>
         <v>4774</v>
       </c>
-      <c r="AD71" s="2">
-        <f t="shared" si="33"/>
+      <c r="AH72" s="2">
+        <f t="shared" si="38"/>
         <v>4612</v>
       </c>
-      <c r="AE71" s="2">
-        <f t="shared" si="33"/>
+      <c r="AI72" s="2">
+        <f t="shared" si="38"/>
         <v>7594</v>
       </c>
-      <c r="AF71" s="2">
-        <f t="shared" si="33"/>
+      <c r="AJ72" s="2">
+        <f t="shared" si="38"/>
         <v>7487</v>
       </c>
     </row>
